--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_1_8.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_1_8.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222828.7510725867</v>
+        <v>232770.1615244462</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5413711.842050619</v>
+        <v>5117489.51767665</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22726010.95505212</v>
+        <v>22435683.45493321</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3915832.239858635</v>
+        <v>4042394.47710314</v>
       </c>
     </row>
     <row r="11">
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2201,19 +2201,19 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2277,19 +2277,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>22.56635248423081</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="24">
@@ -2432,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2678,19 +2678,19 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
     </row>
     <row r="28">
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2833,16 +2833,16 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2921,13 +2921,13 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="31">
@@ -2994,16 +2994,16 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3025,13 +3025,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3101,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3228,19 +3228,19 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3471,10 +3471,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="39">
@@ -3578,13 +3578,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3696,16 +3696,16 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3736,13 +3736,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="42">
@@ -3857,19 +3857,19 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3900,16 +3900,16 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>27.413711578255</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>52.77779986093952</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="44">
@@ -9384,16 +9384,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M20" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N20" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O20" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -9460,16 +9460,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O21" t="n">
         <v>142.5962444444444</v>
@@ -9478,7 +9478,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9542,16 +9542,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M22" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N22" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O22" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P22" t="n">
         <v>135.0065633140411</v>
@@ -9618,16 +9618,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L23" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M23" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O23" t="n">
         <v>230.0982114216867</v>
@@ -9697,13 +9697,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N24" t="n">
         <v>131.3417120833333</v>
@@ -9715,7 +9715,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9779,16 +9779,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M25" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N25" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O25" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P25" t="n">
         <v>135.0065633140411</v>
@@ -9861,16 +9861,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P26" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,16 +9934,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O27" t="n">
         <v>142.5962444444444</v>
@@ -10016,16 +10016,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M28" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N28" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O28" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P28" t="n">
         <v>135.0065633140411</v>
@@ -10092,16 +10092,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L29" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M29" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N29" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O29" t="n">
         <v>230.0982114216867</v>
@@ -10174,7 +10174,7 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -10183,13 +10183,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,16 +10253,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M31" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O31" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P31" t="n">
         <v>135.0065633140411</v>
@@ -10329,19 +10329,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M32" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O32" t="n">
-        <v>230.0982114216867</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -10408,16 +10408,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O33" t="n">
         <v>142.5962444444444</v>
@@ -10490,16 +10490,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M34" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N34" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O34" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P34" t="n">
         <v>135.0065633140411</v>
@@ -10569,16 +10569,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O35" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P35" t="n">
         <v>231.2329957552695</v>
@@ -10645,16 +10645,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O36" t="n">
         <v>142.5962444444444</v>
@@ -10727,16 +10727,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M37" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N37" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O37" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P37" t="n">
         <v>135.0065633140411</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>220.0898510449805</v>
+        <v>244.6749789590202</v>
       </c>
       <c r="L38" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
@@ -10818,7 +10818,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P38" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,16 +10882,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O39" t="n">
         <v>142.5962444444444</v>
@@ -10964,16 +10964,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M40" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N40" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O40" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P40" t="n">
         <v>135.0065633140411</v>
@@ -11040,10 +11040,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L41" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M41" t="n">
         <v>230.3462332272727</v>
@@ -11052,10 +11052,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11122,19 +11122,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N42" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -11201,16 +11201,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M43" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N43" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O43" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P43" t="n">
         <v>135.0065633140411</v>
@@ -23941,7 +23941,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>392.7363850309042</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23983,16 +23983,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3456529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y20" t="n">
         <v>386.2379386560536</v>
@@ -24059,19 +24059,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>183.2066327192466</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24135,19 +24135,19 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>224.0165980369723</v>
+        <v>201.4502455527414</v>
       </c>
       <c r="T22" t="n">
-        <v>227.9455894282815</v>
+        <v>202.3252982336507</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>260.9027071419601</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24181,7 +24181,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>326.8991488460811</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
@@ -24208,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
@@ -24226,13 +24226,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y23" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="24">
@@ -24290,10 +24290,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>146.062879909207</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
@@ -24302,10 +24302,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>229.1286306766888</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>179.8319801819373</v>
+        <v>157.2656276977065</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24333,10 +24333,10 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F25" t="n">
-        <v>145.4210480229312</v>
+        <v>119.8007568283004</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24381,7 +24381,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W25" t="n">
         <v>286.522998336591</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>357.1135504688497</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24415,10 +24415,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H26" t="n">
-        <v>339.4748021157671</v>
+        <v>326.8991488460811</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
@@ -24466,7 +24466,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24536,19 +24536,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W27" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>183.1163432930735</v>
       </c>
     </row>
     <row r="28">
@@ -24558,13 +24558,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>179.8319801819373</v>
+        <v>154.2116889873065</v>
       </c>
       <c r="C28" t="n">
-        <v>167.2468210986278</v>
+        <v>141.626529903997</v>
       </c>
       <c r="D28" t="n">
-        <v>148.6154730182124</v>
+        <v>126.0491205339815</v>
       </c>
       <c r="E28" t="n">
         <v>146.4339626465692</v>
@@ -24615,7 +24615,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24691,16 +24691,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>200.5294970799005</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>302.1319672755041</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X29" t="n">
         <v>369.731100678469</v>
@@ -24719,7 +24719,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>147.0882077936849</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24779,13 +24779,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>229.1286306766888</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>180.0624045826735</v>
       </c>
     </row>
     <row r="31">
@@ -24852,16 +24852,16 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3190293564909</v>
+        <v>263.7526768722601</v>
       </c>
       <c r="V31" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>260.9027071419601</v>
       </c>
       <c r="X31" t="n">
-        <v>225.7096553890372</v>
+        <v>200.0893641944063</v>
       </c>
       <c r="Y31" t="n">
         <v>218.5846533520948</v>
@@ -24883,13 +24883,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>359.3640175880309</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24928,7 +24928,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
@@ -24959,10 +24959,10 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>121.8247743700079</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>135.0787279711701</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
@@ -25001,13 +25001,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U33" t="n">
         <v>225.9413820809748</v>
@@ -25086,19 +25086,19 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>205.3792369440507</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V34" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W34" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
-        <v>225.7096553890372</v>
+        <v>200.0893641944063</v>
       </c>
       <c r="Y34" t="n">
         <v>218.5846533520948</v>
@@ -25123,13 +25123,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>406.8760457417114</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G35" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>326.8991488460811</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,10 +25156,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25196,13 +25196,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>121.8247743700079</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>132.0247892607701</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>122.502859909153</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -25244,7 +25244,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
@@ -25269,7 +25269,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>179.8319801819373</v>
+        <v>154.2116889873065</v>
       </c>
       <c r="C37" t="n">
         <v>167.2468210986278</v>
@@ -25284,7 +25284,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>145.4246268742279</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
@@ -25329,10 +25329,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W37" t="n">
-        <v>286.522998336591</v>
+        <v>260.9027071419601</v>
       </c>
       <c r="X37" t="n">
         <v>225.7096553890372</v>
@@ -25348,7 +25348,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>370.1581883937945</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
@@ -25393,10 +25393,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
@@ -25414,10 +25414,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="39">
@@ -25436,13 +25436,13 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>132.0247892607701</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>114.7771646789798</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
@@ -25490,7 +25490,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25554,16 +25554,16 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S40" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T40" t="n">
-        <v>227.9455894282815</v>
+        <v>202.3252982336507</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>263.7526768722601</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25594,13 +25594,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
@@ -25648,13 +25648,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>349.240968717413</v>
+        <v>326.6746162331822</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="42">
@@ -25715,19 +25715,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>149.116818619607</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U42" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H43" t="n">
-        <v>162.2271725074396</v>
+        <v>139.6608200232087</v>
       </c>
       <c r="I43" t="n">
-        <v>155.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J43" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K43" t="n">
         <v>22.26949182588285</v>
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887401</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887401</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887403</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887401</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.98658874</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887402</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887401</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>338648.3274240561</v>
+        <v>361518.9865887403</v>
       </c>
     </row>
     <row r="16">
@@ -26261,7 +26261,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43002.96221257857</v>
+        <v>43002.96221257855</v>
       </c>
       <c r="C2" t="n">
         <v>43002.96221257855</v>
@@ -26276,31 +26276,31 @@
         <v>43002.96221257855</v>
       </c>
       <c r="G2" t="n">
-        <v>43002.96221257856</v>
+        <v>43002.96221257855</v>
       </c>
       <c r="H2" t="n">
-        <v>43002.96221257857</v>
+        <v>45906.23721376774</v>
       </c>
       <c r="I2" t="n">
-        <v>43002.96221257856</v>
+        <v>45906.23721376774</v>
       </c>
       <c r="J2" t="n">
-        <v>43002.96221257856</v>
+        <v>45906.23721376774</v>
       </c>
       <c r="K2" t="n">
-        <v>43002.96221257857</v>
+        <v>45906.23721376773</v>
       </c>
       <c r="L2" t="n">
-        <v>43002.96221257856</v>
+        <v>45906.23721376774</v>
       </c>
       <c r="M2" t="n">
-        <v>43002.96221257857</v>
+        <v>45906.23721376774</v>
       </c>
       <c r="N2" t="n">
-        <v>43002.96221257857</v>
+        <v>45906.23721376773</v>
       </c>
       <c r="O2" t="n">
-        <v>43002.96221257857</v>
+        <v>45906.23721376773</v>
       </c>
       <c r="P2" t="n">
         <v>43002.96221257855</v>
@@ -26331,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>6912.585146932151</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="C4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="D4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="E4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="F4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="G4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="H4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.004316546619</v>
       </c>
       <c r="I4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.00431654662</v>
       </c>
       <c r="J4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.004316546619</v>
       </c>
       <c r="K4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.00431654662</v>
       </c>
       <c r="L4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.00431654662</v>
       </c>
       <c r="M4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.004316546619</v>
       </c>
       <c r="N4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.00431654662</v>
       </c>
       <c r="O4" t="n">
-        <v>5375.37027657232</v>
+        <v>4511.004316546619</v>
       </c>
       <c r="P4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
     </row>
     <row r="5">
@@ -26435,28 +26435,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3999.991936006249</v>
+        <v>5175.854184006428</v>
       </c>
       <c r="C6" t="n">
-        <v>3999.991936006234</v>
+        <v>5175.854184006428</v>
       </c>
       <c r="D6" t="n">
-        <v>3999.991936006234</v>
+        <v>5175.854184006428</v>
       </c>
       <c r="E6" t="n">
-        <v>37627.59193600623</v>
+        <v>38803.45418400643</v>
       </c>
       <c r="F6" t="n">
-        <v>37627.59193600623</v>
+        <v>38803.45418400643</v>
       </c>
       <c r="G6" t="n">
-        <v>37627.59193600624</v>
+        <v>38803.45418400643</v>
       </c>
       <c r="H6" t="n">
-        <v>37627.59193600625</v>
+        <v>32924.93404565541</v>
       </c>
       <c r="I6" t="n">
-        <v>37627.59193600624</v>
+        <v>39837.51919258757</v>
       </c>
       <c r="J6" t="n">
-        <v>37627.59193600624</v>
+        <v>39837.51919258757</v>
       </c>
       <c r="K6" t="n">
-        <v>37627.59193600625</v>
+        <v>39837.51919258756</v>
       </c>
       <c r="L6" t="n">
-        <v>37627.59193600624</v>
+        <v>39837.51919258757</v>
       </c>
       <c r="M6" t="n">
-        <v>37627.59193600625</v>
+        <v>39837.51919258757</v>
       </c>
       <c r="N6" t="n">
-        <v>37627.59193600625</v>
+        <v>39837.51919258756</v>
       </c>
       <c r="O6" t="n">
-        <v>37627.59193600625</v>
+        <v>39837.51919258756</v>
       </c>
       <c r="P6" t="n">
-        <v>37627.59193600623</v>
+        <v>38803.45418400643</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
   </sheetData>
@@ -36039,16 +36039,16 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36115,16 +36115,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -36133,7 +36133,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36197,16 +36197,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -36273,16 +36273,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36352,13 +36352,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -36370,7 +36370,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36434,16 +36434,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -36516,16 +36516,16 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,16 +36589,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -36671,16 +36671,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -36747,16 +36747,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36829,7 +36829,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -36838,13 +36838,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36908,16 +36908,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -36984,19 +36984,19 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37063,16 +37063,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -37145,16 +37145,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -37224,16 +37224,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37300,16 +37300,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -37382,16 +37382,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37473,7 +37473,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,16 +37537,16 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -37619,16 +37619,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -37695,10 +37695,10 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -37707,10 +37707,10 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37777,19 +37777,19 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37856,16 +37856,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
